--- a/config/excel/upgrades.xlsx
+++ b/config/excel/upgrades.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:Q39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>每5秒获得1层护盾</t>
+          <t>每15秒获得1层护盾（每层-1秒，最多5层）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2756,6 +2756,234 @@
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>elem_fire_plus</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>炎魂</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>🔥</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>火元素伤害 +30%/级 (燃烧/火球/火墙均生效)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fire_enhance</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>elem_ice_plus</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>冰魂</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>❄️</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>冰元素伤害 +30%/级 (水龙卷/冰冻爆破/冰霜轨迹均生效)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ice_enhance</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>elem_thunder_plus</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>雷魂</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>⚡</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>雷元素伤害 +30%/级 (雷链/天雷均生效)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>thunder_enhance</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>elem_poison_plus</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>毒魂</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>🐍</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>毒元素伤害 +30%/级 (未来毒系技能/DoT生效)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>poison_enhance</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
